--- a/data/output/maize_community_survey_import.xlsx
+++ b/data/output/maize_community_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM5"/>
+  <dimension ref="A1:CM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,6 +2475,339 @@
       <c r="CL5" t="inlineStr"/>
       <c r="CM5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/maize_community_survey_import.xlsx
+++ b/data/output/maize_community_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM3"/>
+  <dimension ref="A1:CM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1729,6 +1729,227 @@
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/maize_community_survey_import.xlsx
+++ b/data/output/maize_community_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM4"/>
+  <dimension ref="A1:CM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,6 +1950,215 @@
       <c r="CL4" t="inlineStr"/>
       <c r="CM4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/maize_community_survey_import.xlsx
+++ b/data/output/maize_community_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM5"/>
+  <dimension ref="A1:CM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2159,6 +2159,275 @@
       <c r="CL5" t="inlineStr"/>
       <c r="CM5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/output/maize_community_survey_import.xlsx
+++ b/data/output/maize_community_survey_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM6"/>
+  <dimension ref="A1:CM8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2428,616 @@
       <c r="CL6" t="inlineStr"/>
       <c r="CM6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>R_papertrail_0001</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>paper</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
